--- a/Section 4.1/Data_section4.1.xlsx
+++ b/Section 4.1/Data_section4.1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Comsol_Tut\EquationBasedModelling\HTO_paper_models\latest_model_tcd\Neom_report_models\Publication Models\modified_model\Optimization_study\saved data\Joule_submission_docs\Section 3.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KUNTEAM\Documents\GitHub\Physics-informed-multiscale-optimization-of-renewable-powered-alkaline-water-electrolysis\Section 4.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779B5136-53DF-42FA-8626-24E96230581E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6224BB4B-344B-47C0-B243-6A7613207DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{7C88D86B-F107-4116-B17D-B8DFC6C89132}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="70">
   <si>
     <t>M_H2</t>
   </si>
@@ -243,6 +243,9 @@
   </si>
   <si>
     <t>Stack SEC and efficincies (Fig. 4a)</t>
+  </si>
+  <si>
+    <t>j</t>
   </si>
 </sst>
 </file>
@@ -836,20 +839,23 @@
       <c r="U9">
         <v>0.34139999999999998</v>
       </c>
+      <c r="Z9" t="s">
+        <v>3</v>
+      </c>
       <c r="AA9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE9" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="2:46" x14ac:dyDescent="0.25">
@@ -905,22 +911,22 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>0.17307</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>0.1908</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>0.52266000000000001</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>9.3289999999999998E-2</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>0.21767</v>
       </c>
       <c r="AE10">
-        <v>0.99750000000000005</v>
+        <v>-1.379E-2</v>
       </c>
     </row>
     <row r="11" spans="2:46" x14ac:dyDescent="0.25">
@@ -976,22 +982,22 @@
         <v>33</v>
       </c>
       <c r="Z11">
-        <v>-0.19328999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>3.7100000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>-0.51053000000000004</v>
+        <v>0</v>
       </c>
       <c r="AC11">
         <v>0</v>
       </c>
       <c r="AD11">
-        <v>7.4230000000000004E-2</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>0.39457999999999999</v>
+        <v>0.99750000000000005</v>
       </c>
     </row>
     <row r="12" spans="2:46" x14ac:dyDescent="0.25">
@@ -1047,22 +1053,22 @@
         <v>34</v>
       </c>
       <c r="Z12">
-        <v>0.10460999999999999</v>
+        <v>-0.36</v>
       </c>
       <c r="AA12">
-        <v>0.43320999999999998</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="AB12">
-        <v>0.35696</v>
+        <v>-0.438</v>
       </c>
       <c r="AC12">
-        <v>6.7879999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="AE12">
-        <v>-0.15260000000000001</v>
+        <v>0.33900000000000002</v>
       </c>
     </row>
     <row r="13" spans="2:46" x14ac:dyDescent="0.25">
@@ -1118,22 +1124,22 @@
         <v>35</v>
       </c>
       <c r="Z13">
-        <v>6.5700000000000003E-3</v>
+        <v>0.193</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="AB13">
-        <v>1.25E-3</v>
+        <v>0.314</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="AD13">
-        <v>-0.44078000000000001</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>-0.56771000000000005</v>
+        <v>-0.13200000000000001</v>
       </c>
     </row>
     <row r="14" spans="2:46" x14ac:dyDescent="0.25">
@@ -1189,22 +1195,22 @@
         <v>36</v>
       </c>
       <c r="Z14">
-        <v>-0.21415999999999999</v>
+        <v>1.6E-2</v>
       </c>
       <c r="AA14">
-        <v>-0.28325</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>-0.25924999999999998</v>
+        <v>1.25E-3</v>
       </c>
       <c r="AC14">
-        <v>-4.607E-2</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>-0.48699999999999999</v>
       </c>
       <c r="AE14">
-        <v>0.27376</v>
+        <v>-0.51500000000000001</v>
       </c>
     </row>
     <row r="15" spans="2:46" x14ac:dyDescent="0.25">
@@ -1260,22 +1266,22 @@
         <v>37</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
       <c r="AA15">
-        <v>-0.99614000000000003</v>
+        <v>-0.313</v>
       </c>
       <c r="AB15">
-        <v>-1.1100000000000001E-3</v>
+        <v>-0.24199999999999999</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>-3.4000000000000002E-2</v>
       </c>
       <c r="AD15">
-        <v>1.25E-3</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>4.2599999999999999E-3</v>
+        <v>0.20200000000000001</v>
       </c>
     </row>
     <row r="16" spans="2:46" x14ac:dyDescent="0.25">
@@ -1331,22 +1337,22 @@
         <v>38</v>
       </c>
       <c r="Z16">
-        <v>3.7299999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>-0.23604</v>
+        <v>-0.99614000000000003</v>
       </c>
       <c r="AB16">
-        <v>1.187E-2</v>
+        <v>-3.0000000000000001E-3</v>
       </c>
       <c r="AC16">
-        <v>2.1900000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="AE16">
-        <v>-0.74617999999999995</v>
+        <v>7.0000000000000001E-3</v>
       </c>
     </row>
     <row r="17" spans="2:31" x14ac:dyDescent="0.25">
@@ -1402,22 +1408,22 @@
         <v>39</v>
       </c>
       <c r="Z17">
-        <v>0.25007000000000001</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="AA17" s="5">
-        <v>4.8799999999999999E-4</v>
+        <v>-0.17100000000000001</v>
       </c>
       <c r="AB17">
-        <v>0.52942999999999996</v>
+        <v>1.4E-2</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2E-3</v>
       </c>
       <c r="AD17">
         <v>0</v>
       </c>
       <c r="AE17">
-        <v>-0.33468999999999999</v>
+        <v>-0.81</v>
       </c>
     </row>
     <row r="18" spans="2:31" x14ac:dyDescent="0.25">
@@ -1473,13 +1479,13 @@
         <v>40</v>
       </c>
       <c r="Z18">
-        <v>0</v>
-      </c>
-      <c r="AA18">
-        <v>-1</v>
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="AA18" s="5">
+        <v>4.8799999999999999E-4</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>0.46100000000000002</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -1488,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="AE18" s="5">
-        <v>1.57973E-31</v>
+        <v>-0.29199999999999998</v>
       </c>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.25">
@@ -1544,22 +1550,22 @@
         <v>41</v>
       </c>
       <c r="Z19">
-        <v>-1.7409999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>1.61E-2</v>
+        <v>-1</v>
       </c>
       <c r="AB19">
-        <v>-2.282E-2</v>
+        <v>0</v>
       </c>
       <c r="AC19">
         <v>0</v>
       </c>
       <c r="AD19">
-        <v>0.33445000000000003</v>
-      </c>
-      <c r="AE19">
-        <v>0.65154000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="AE19" s="5">
+        <v>1.57973E-31</v>
       </c>
     </row>
     <row r="20" spans="2:31" x14ac:dyDescent="0.25">
@@ -1615,22 +1621,22 @@
         <v>42</v>
       </c>
       <c r="Z20">
-        <v>2.3500000000000001E-3</v>
+        <v>-3.4000000000000002E-2</v>
       </c>
       <c r="AA20">
-        <v>1.8679999999999999E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AB20">
-        <v>1.8270000000000002E-2</v>
+        <v>-1.7999999999999999E-2</v>
       </c>
       <c r="AC20">
-        <v>7.5900000000000004E-3</v>
+        <v>0</v>
       </c>
       <c r="AD20">
-        <v>0.52998000000000001</v>
+        <v>0.36099999999999999</v>
       </c>
       <c r="AE20">
-        <v>0.46693000000000001</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="21" spans="2:31" x14ac:dyDescent="0.25">
@@ -1686,22 +1692,22 @@
         <v>1</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.3500000000000001E-3</v>
       </c>
       <c r="AA21">
-        <v>2.3900000000000002E-3</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="AB21">
-        <v>7.9000000000000008E-3</v>
+        <v>0.03</v>
       </c>
       <c r="AC21">
-        <v>3.65E-3</v>
+        <v>7.5900000000000004E-3</v>
       </c>
       <c r="AD21">
-        <v>0.51678000000000002</v>
+        <v>0.56599999999999995</v>
       </c>
       <c r="AE21">
-        <v>0.51246999999999998</v>
+        <v>0.40500000000000003</v>
       </c>
     </row>
     <row r="22" spans="2:31" x14ac:dyDescent="0.25">
@@ -1753,6 +1759,24 @@
       <c r="U22">
         <v>2.21</v>
       </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>2.3900000000000002E-3</v>
+      </c>
+      <c r="AB22">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="AC22">
+        <v>3.65E-3</v>
+      </c>
+      <c r="AD22">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AE22">
+        <v>0.46</v>
+      </c>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B23">
@@ -2152,31 +2176,31 @@
         <v>3</v>
       </c>
       <c r="W30">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="X30">
-        <v>0.24</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="Y30">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="Z30">
         <v>2.8900000000000002E-3</v>
       </c>
       <c r="AA30">
-        <v>0.22</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AB30">
-        <v>-0.22</v>
+        <v>-0.31</v>
       </c>
       <c r="AC30">
         <v>2.8E-3</v>
       </c>
       <c r="AD30">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AE30">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="31" spans="2:31" x14ac:dyDescent="0.25">
@@ -2226,31 +2250,31 @@
         <v>4</v>
       </c>
       <c r="W31">
-        <v>0.10911</v>
+        <v>0.19</v>
       </c>
       <c r="X31">
-        <v>0.05</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="Y31">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="Z31">
-        <v>0.54063000000000005</v>
+        <v>0.65</v>
       </c>
       <c r="AA31">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AB31">
-        <v>-0.18618999999999999</v>
+        <v>-0.26</v>
       </c>
       <c r="AC31">
         <v>-0.95</v>
       </c>
       <c r="AD31">
-        <v>0.15</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AE31">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.25">
@@ -2300,31 +2324,31 @@
         <v>5</v>
       </c>
       <c r="W32">
-        <v>1.226E-2</v>
+        <v>0.02</v>
       </c>
       <c r="X32">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="Y32">
-        <v>0.56000000000000005</v>
+        <v>0.49</v>
       </c>
       <c r="Z32">
         <v>0.02</v>
       </c>
       <c r="AA32">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="AB32">
-        <v>-0.57999999999999996</v>
+        <v>-0.46</v>
       </c>
       <c r="AC32">
         <v>1.48E-3</v>
       </c>
       <c r="AD32">
-        <v>0.15976000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="AE32">
-        <v>0.14000000000000001</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="33" spans="2:31" x14ac:dyDescent="0.25">
@@ -2374,7 +2398,7 @@
         <v>6</v>
       </c>
       <c r="W33">
-        <v>1.2840000000000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="X33">
         <v>0</v>
@@ -2448,31 +2472,31 @@
         <v>7</v>
       </c>
       <c r="W34">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="X34">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="Y34">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="Z34">
-        <v>0.47210999999999997</v>
+        <v>0.36</v>
       </c>
       <c r="AA34">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="AB34">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="AC34">
         <v>0.05</v>
       </c>
       <c r="AD34">
-        <v>0.44568999999999998</v>
+        <v>0.31</v>
       </c>
       <c r="AE34">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="35" spans="2:31" x14ac:dyDescent="0.25">
@@ -2755,11 +2779,11 @@
         <v>18</v>
       </c>
       <c r="Y40">
-        <v>4933037</v>
+        <v>4400687</v>
       </c>
       <c r="Z40">
         <f>Y40/(SUM(Y40:Y42))*100</f>
-        <v>11.575215446275882</v>
+        <v>11.688822425287348</v>
       </c>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.25">
@@ -2809,11 +2833,11 @@
         <v>19</v>
       </c>
       <c r="Y41">
-        <v>10278400</v>
+        <v>8799690</v>
       </c>
       <c r="Z41">
         <f>Y41/(SUM(Y40:Y42))*100</f>
-        <v>24.1179408228647</v>
+        <v>23.373171917833925</v>
       </c>
     </row>
     <row r="42" spans="2:31" x14ac:dyDescent="0.25">
@@ -2862,12 +2886,12 @@
       <c r="X42" t="s">
         <v>20</v>
       </c>
-      <c r="Y42">
-        <v>27405800</v>
+      <c r="Y42" s="5">
+        <v>24448300</v>
       </c>
       <c r="Z42">
         <f>Y42/(SUM(Y40:Y42))*100</f>
-        <v>64.306843730859413</v>
+        <v>64.93800565687873</v>
       </c>
     </row>
     <row r="43" spans="2:31" x14ac:dyDescent="0.25">
@@ -3020,7 +3044,7 @@
       </c>
       <c r="Z45">
         <f>Y45/(SUM(Y45:Y53))*100</f>
-        <v>22.273006361935867</v>
+        <v>24.968495251732403</v>
       </c>
     </row>
     <row r="46" spans="2:31" x14ac:dyDescent="0.25">
@@ -3074,7 +3098,7 @@
       </c>
       <c r="Z46">
         <f>Y46/(SUM($Y$45:$Y$53))*100</f>
-        <v>13.941479536270565</v>
+        <v>15.628683436214894</v>
       </c>
     </row>
     <row r="47" spans="2:31" x14ac:dyDescent="0.25">
@@ -3127,8 +3151,8 @@
         <v>140.4</v>
       </c>
       <c r="Z47">
-        <f t="shared" ref="Z47:Z53" si="0">Y47/(SUM($Y$45:$Y$53))*100</f>
-        <v>9.1125871829254539</v>
+        <f>Y47/(SUM($Y$45:$Y$53))*100</f>
+        <v>10.21539643596169</v>
       </c>
       <c r="AD47" s="1"/>
     </row>
@@ -3182,8 +3206,8 @@
         <v>114</v>
       </c>
       <c r="Z48">
-        <f t="shared" si="0"/>
-        <v>7.3991092510933161</v>
+        <f>Y48/(SUM($Y$45:$Y$53))*100</f>
+        <v>8.2945526616782956</v>
       </c>
       <c r="AC48" s="3"/>
       <c r="AD48" s="3"/>
@@ -3239,8 +3263,8 @@
         <v>62.2</v>
       </c>
       <c r="Z49">
-        <f t="shared" si="0"/>
-        <v>4.0370578545438978</v>
+        <f>Y49/(SUM($Y$45:$Y$53))*100</f>
+        <v>4.525624346985877</v>
       </c>
     </row>
     <row r="50" spans="2:26" x14ac:dyDescent="0.25">
@@ -3293,8 +3317,8 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="Z50">
-        <f t="shared" si="0"/>
-        <v>0.63606377772556577</v>
+        <f>Y50/(SUM($Y$45:$Y$53))*100</f>
+        <v>0.7130404919688359</v>
       </c>
     </row>
     <row r="51" spans="2:26" x14ac:dyDescent="0.25">
@@ -3347,8 +3371,8 @@
         <v>7.66</v>
       </c>
       <c r="Z51">
-        <f t="shared" si="0"/>
-        <v>0.49716821809977896</v>
+        <f>Y51/(SUM($Y$45:$Y$53))*100</f>
+        <v>0.55733573147768189</v>
       </c>
     </row>
     <row r="52" spans="2:26" x14ac:dyDescent="0.25">
@@ -3401,8 +3425,8 @@
         <v>199</v>
       </c>
       <c r="Z52">
-        <f t="shared" si="0"/>
-        <v>12.915988955855875</v>
+        <f>Y52/(SUM($Y$45:$Y$53))*100</f>
+        <v>14.47908754099983</v>
       </c>
     </row>
     <row r="53" spans="2:26" x14ac:dyDescent="0.25">
@@ -3452,11 +3476,11 @@
         <v>8</v>
       </c>
       <c r="Y53">
-        <v>449.7</v>
+        <v>283.37</v>
       </c>
       <c r="Z53">
-        <f t="shared" si="0"/>
-        <v>29.18753886154969</v>
+        <f>Y53/(SUM($Y$45:$Y$53))*100</f>
+        <v>20.617784102980512</v>
       </c>
     </row>
     <row r="54" spans="2:26" x14ac:dyDescent="0.25">
@@ -3504,7 +3528,7 @@
       </c>
       <c r="Z54">
         <f>SUM(Z45:Z53)</f>
-        <v>100</v>
+        <v>100.00000000000001</v>
       </c>
     </row>
     <row r="55" spans="2:26" x14ac:dyDescent="0.25">
